--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-08-2025.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.87</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -704,7 +704,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£12.13</t>
+          <t>£12.01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -825,7 +825,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£15.75</t>
+          <t>£15.59</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£20.60</t>
+          <t>£20.39</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£22.24</t>
+          <t>£22.02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£22.57</t>
+          <t>£22.34</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£25.79</t>
+          <t>£25.53</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£27.95</t>
+          <t>£27.67</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£27.45</t>
+          <t>£27.18</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£33.72</t>
+          <t>£33.38</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£41.10</t>
+          <t>£40.69</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£41.93</t>
+          <t>£41.51</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£41.86</t>
+          <t>£41.44</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>£716.82</t>
+          <t>£709.65</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>£899.89</t>
+          <t>£890.89</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>£29.28</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>£36.11</t>
+          <t>£35.00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£39.21</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>£43.75</t>
+          <t>£43.31</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>£44.43</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>£47.99</t>
+          <t>£47.51</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>£44.02</t>
+          <t>£43.58</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
-	GetHandleVerifier [0x0x7ff6d501eb70+79568]
-	(No symbol) [0x0x7ff6d4dbc0fa]
-	(No symbol) [0x0x7ff6d4e12a96]
-	(No symbol) [0x0x7ff6d4e12d4c]
-	(No symbol) [0x0x7ff6d4e66017]
-	(No symbol) [0x0x7ff6d4e3accf]
-	(No symbol) [0x0x7ff6d4e62e24]
-	(No symbol) [0x0x7ff6d4e3aa63]
-	(No symbol) [0x0x7ff6d4e03c91]
-	(No symbol) [0x0x7ff6d4e04a23]
-	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
-	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
-	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
-	GetHandleVerifier [0x0x7ff6d503836e+184014]
-	GetHandleVerifier [0x0x7ff6d504024f+216495]
-	GetHandleVerifier [0x0x7ff6d50270c4+113700]
-	GetHandleVerifier [0x0x7ff6d5027279+114137]
-	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	GetHandleVerifier [0x0x7ff613d578d5+2802741]
+	GetHandleVerifier [0x0x7ff613abeb70+79568]
+	(No symbol) [0x0x7ff61385c0fa]
+	(No symbol) [0x0x7ff6138b2a96]
+	(No symbol) [0x0x7ff6138b2d4c]
+	(No symbol) [0x0x7ff613906017]
+	(No symbol) [0x0x7ff6138daccf]
+	(No symbol) [0x0x7ff613902e24]
+	(No symbol) [0x0x7ff6138daa63]
+	(No symbol) [0x0x7ff6138a3c91]
+	(No symbol) [0x0x7ff6138a4a23]
+	GetHandleVerifier [0x0x7ff613d82ced+2979917]
+	GetHandleVerifier [0x0x7ff613d7d0f3+2956371]
+	GetHandleVerifier [0x0x7ff613d9acbd+3078173]
+	GetHandleVerifier [0x0x7ff613ad836e+184014]
+	GetHandleVerifier [0x0x7ff613ae024f+216495]
+	GetHandleVerifier [0x0x7ff613ac70c4+113700]
+	GetHandleVerifier [0x0x7ff613ac7279+114137]
+	GetHandleVerifier [0x0x7ff613aadf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>£1152.0</t>
+          <t>£1140.48</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>£1280.0</t>
+          <t>£1267.2</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>£1213.28</t>
+          <t>£1201.12</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
